--- a/docs/downloads/11/tbl_cultures_touchees_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_alaotra_tous.xlsx
@@ -1287,12 +1287,6 @@
           <t>mais</t>
         </is>
       </c>
-      <c r="C52">
-        <v>4</v>
-      </c>
-      <c r="D52">
-        <v>7.8</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1305,12 +1299,6 @@
           <t>tabac</t>
         </is>
       </c>
-      <c r="C53">
-        <v>4</v>
-      </c>
-      <c r="D53">
-        <v>4.1</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1323,12 +1311,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C54">
-        <v>4</v>
-      </c>
-      <c r="D54">
-        <v>6.2</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1341,12 +1323,6 @@
           <t>mais</t>
         </is>
       </c>
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55">
-        <v>6.2</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1359,12 +1335,6 @@
           <t>cane à sucre</t>
         </is>
       </c>
-      <c r="C56">
-        <v>4</v>
-      </c>
-      <c r="D56">
-        <v>5.7</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1377,12 +1347,6 @@
           <t>mais</t>
         </is>
       </c>
-      <c r="C57">
-        <v>4</v>
-      </c>
-      <c r="D57">
-        <v>5.7</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1395,12 +1359,6 @@
           <t>Choux</t>
         </is>
       </c>
-      <c r="C58">
-        <v>4</v>
-      </c>
-      <c r="D58">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1413,12 +1371,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C59">
-        <v>3</v>
-      </c>
-      <c r="D59">
-        <v>5.7</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1431,12 +1383,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
-      <c r="D60">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1449,12 +1395,6 @@
           <t>arachide</t>
         </is>
       </c>
-      <c r="C61">
-        <v>3</v>
-      </c>
-      <c r="D61">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1467,12 +1407,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C62">
-        <v>3</v>
-      </c>
-      <c r="D62">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1485,12 +1419,6 @@
           <t>Courgette</t>
         </is>
       </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
-      <c r="D63">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1503,12 +1431,6 @@
           <t>Mangue</t>
         </is>
       </c>
-      <c r="C64">
-        <v>3</v>
-      </c>
-      <c r="D64">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1521,12 +1443,6 @@
           <t>manioc</t>
         </is>
       </c>
-      <c r="C65">
-        <v>3</v>
-      </c>
-      <c r="D65">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1539,12 +1455,6 @@
           <t>Concombre</t>
         </is>
       </c>
-      <c r="C66">
-        <v>3</v>
-      </c>
-      <c r="D66">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1557,12 +1467,6 @@
           <t>taro</t>
         </is>
       </c>
-      <c r="C67">
-        <v>3</v>
-      </c>
-      <c r="D67">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1575,12 +1479,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C68">
-        <v>3</v>
-      </c>
-      <c r="D68">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1593,12 +1491,6 @@
           <t>Carotte</t>
         </is>
       </c>
-      <c r="C69">
-        <v>3</v>
-      </c>
-      <c r="D69">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1611,12 +1503,6 @@
           <t>Petits pois</t>
         </is>
       </c>
-      <c r="C70">
-        <v>3</v>
-      </c>
-      <c r="D70">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1629,12 +1515,6 @@
           <t>Banane</t>
         </is>
       </c>
-      <c r="C71">
-        <v>2</v>
-      </c>
-      <c r="D71">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1647,12 +1527,6 @@
           <t>Pois de terre</t>
         </is>
       </c>
-      <c r="C72">
-        <v>2</v>
-      </c>
-      <c r="D72">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1665,12 +1539,6 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="C73">
-        <v>2</v>
-      </c>
-      <c r="D73">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1683,12 +1551,6 @@
           <t>tamarin</t>
         </is>
       </c>
-      <c r="C74">
-        <v>2</v>
-      </c>
-      <c r="D74">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1701,12 +1563,6 @@
           <t>Courgette</t>
         </is>
       </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-      <c r="D75">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1719,12 +1575,6 @@
           <t>Pois de terre</t>
         </is>
       </c>
-      <c r="C76">
-        <v>2</v>
-      </c>
-      <c r="D76">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1737,12 +1587,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C77">
-        <v>2</v>
-      </c>
-      <c r="D77">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1755,12 +1599,6 @@
           <t>Poivron</t>
         </is>
       </c>
-      <c r="C78">
-        <v>2</v>
-      </c>
-      <c r="D78">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1773,12 +1611,6 @@
           <t>Ciboulette</t>
         </is>
       </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
-      <c r="D79">
-        <v>2</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1791,12 +1623,6 @@
           <t>Concombre</t>
         </is>
       </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80">
-        <v>2</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1809,12 +1635,6 @@
           <t>Poivron</t>
         </is>
       </c>
-      <c r="C81">
-        <v>2</v>
-      </c>
-      <c r="D81">
-        <v>2</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1827,12 +1647,6 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="C82">
-        <v>2</v>
-      </c>
-      <c r="D82">
-        <v>2</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1845,12 +1659,6 @@
           <t>Banane</t>
         </is>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1863,12 +1671,6 @@
           <t>Carotte</t>
         </is>
       </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1881,12 +1683,6 @@
           <t>Mangue</t>
         </is>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1899,12 +1695,6 @@
           <t>Pois de terre</t>
         </is>
       </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1917,12 +1707,6 @@
           <t>cane à sucre</t>
         </is>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1935,12 +1719,6 @@
           <t>Banane</t>
         </is>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>2</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1953,12 +1731,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>2</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1971,12 +1743,6 @@
           <t>Haricot vert</t>
         </is>
       </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90">
-        <v>2</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1988,12 +1754,6 @@
         <is>
           <t>Ramboutant</t>
         </is>
-      </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/11/tbl_cultures_touchees_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1651,7 +1651,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1723,7 +1723,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
